--- a/Configs/怪物monster.xlsx
+++ b/Configs/怪物monster.xlsx
@@ -77,49 +77,49 @@
     <t>小型异形</t>
   </si>
   <si>
-    <t>1~30|2~20|131~10000|119~10000</t>
+    <t>1~300|2~20|131~10000|119~10000</t>
   </si>
   <si>
     <t>中型异形</t>
   </si>
   <si>
-    <t>1~60|2~35|131~10000|119~10000</t>
+    <t>1~600|2~35|131~10000|119~10000</t>
   </si>
   <si>
     <t>大型异形</t>
   </si>
   <si>
-    <t>1~100|2~50|131~10000|119~10000</t>
+    <t>1~1000|2~50|131~10000|119~10000</t>
   </si>
   <si>
     <t>异形精锐</t>
   </si>
   <si>
-    <t>1~200|2~60|131~10000|119~10000</t>
+    <t>1~2000|2~60|131~10000|119~10000</t>
   </si>
   <si>
     <t>虚空侍卫</t>
   </si>
   <si>
-    <t>1~350|2~80|131~10000|119~10000</t>
+    <t>1~3500|2~80|131~10000|119~10000</t>
   </si>
   <si>
     <t>虚空领主</t>
   </si>
   <si>
-    <t>1~1000|2~30|121~1000|131~10000|119~10000</t>
+    <t>1~10000|2~30|121~1000|131~10000|119~10000</t>
   </si>
   <si>
     <t>深渊守卫</t>
   </si>
   <si>
-    <t>1~1500|2~40|121~900|131~10000|119~10000</t>
+    <t>1~15000|2~40|121~900|131~10000|119~10000</t>
   </si>
   <si>
     <t>虚空暴君</t>
   </si>
   <si>
-    <t>1~2500|2~50|121~800|131~10000|119~10000</t>
+    <t>1~25000|2~50|121~800|131~10000|119~10000</t>
   </si>
   <si>
     <t>风影守卫</t>
